--- a/relatorio_quebra_hash.xlsx
+++ b/relatorio_quebra_hash.xlsx
@@ -1,44 +1,122 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aluno\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE873094-7CB5-4E90-918A-0440226156C2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Análise" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dados" sheetId="1" r:id="rId1"/>
+    <sheet name="Análise" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" concurrentCalc="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+  <si>
+    <t>Processos</t>
+  </si>
+  <si>
+    <t>Tempo_Limite(s)</t>
+  </si>
+  <si>
+    <t>Tempo_Real(s)</t>
+  </si>
+  <si>
+    <t>PINs_Testados</t>
+  </si>
+  <si>
+    <t>PINs_por_Segundo</t>
+  </si>
+  <si>
+    <t>Speedup</t>
+  </si>
+  <si>
+    <t>Eficiência</t>
+  </si>
+  <si>
+    <t>Percentual_Testado</t>
+  </si>
+  <si>
+    <t>Métrica</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Hash Alvo</t>
+  </si>
+  <si>
+    <t>ca6ae33116b93e57b87810a27296fc36</t>
+  </si>
+  <si>
+    <t>PIN Encontrado</t>
+  </si>
+  <si>
+    <t>NÃO ENCONTRADO</t>
+  </si>
+  <si>
+    <t>Total Combinações</t>
+  </si>
+  <si>
+    <t>1,000,000,000</t>
+  </si>
+  <si>
+    <t>Chunk Size</t>
+  </si>
+  <si>
+    <t>2,000,000</t>
+  </si>
+  <si>
+    <t>Tempo Total</t>
+  </si>
+  <si>
+    <t>313.42s</t>
+  </si>
+  <si>
+    <t>Melhor Performance</t>
+  </si>
+  <si>
+    <t>215,367 PINs/s</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -47,94 +125,120 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C6527367-7262-40B8-AEBF-060C8C1EEE7D}" name="Tabela1" displayName="Tabela1" ref="A1:H6" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="1" tableBorderDxfId="2">
+  <autoFilter ref="A1:H6" xr:uid="{67E9BE07-0B72-4AE1-997E-223DFA2956AA}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{55932EAF-8638-4A3B-B85E-F4BDDBF31AC8}" name="Processos"/>
+    <tableColumn id="2" xr3:uid="{94C9710F-8A11-4DB5-A4D8-CD6C29F6539A}" name="Tempo_Limite(s)"/>
+    <tableColumn id="3" xr3:uid="{3B3F8982-3627-4833-8BDE-D007E0DC43B3}" name="Tempo_Real(s)"/>
+    <tableColumn id="4" xr3:uid="{9D7C4D34-CAFC-4D49-915B-BD8A3129A352}" name="PINs_Testados"/>
+    <tableColumn id="5" xr3:uid="{3105D5C8-F9D3-4641-889F-4E1091BCD6C3}" name="PINs_por_Segundo"/>
+    <tableColumn id="6" xr3:uid="{FCC45BCF-6DD5-4FA2-BD8A-EF66F9E4D683}" name="Speedup"/>
+    <tableColumn id="7" xr3:uid="{002F398F-5CE9-4D62-94E0-45D79A2E67C2}" name="Eficiência"/>
+    <tableColumn id="8" xr3:uid="{14DF6D8B-F9C3-4574-AEEE-B5E9B46DA65D}" name="Percentual_Testado"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -421,282 +525,243 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Processos</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Tempo_Limite(s)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Tempo_Real(s)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PINs_Testados</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>PINs_por_Segundo</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Speedup</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Eficiência</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Percentual_Testado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
-        <v>89.3103</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>89.310299999999998</v>
+      </c>
+      <c r="D2">
         <v>8000000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>89575</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0.8</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>15</v>
       </c>
-      <c r="C3" t="n">
-        <v>55.7188</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>55.718800000000002</v>
+      </c>
+      <c r="D3">
         <v>12000000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>215367</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>1.603</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.801</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="G3">
+        <v>0.80100000000000005</v>
+      </c>
+      <c r="H3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>4</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>7.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>55.8447</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>55.844700000000003</v>
+      </c>
+      <c r="D4">
         <v>4000000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>71627</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>1.599</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0.4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>3.75</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>56.128</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>1.591</v>
       </c>
-      <c r="G5" t="n">
-        <v>0.199</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="G5">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>12</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>2.5</v>
       </c>
-      <c r="C6" t="n">
-        <v>56.4188</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>56.418799999999997</v>
+      </c>
+      <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>1.583</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="G6">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Métrica</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hash Alvo</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ca6ae33116b93e57b87810a27296fc36</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PIN Encontrado</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NÃO ENCONTRADO</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Total Combinações</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1,000,000,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chunk Size</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2,000,000</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tempo Total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>313.42s</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Melhor Performance</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>215,367 PINs/s</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
